--- a/AAII_Financials/Quarterly/ISRG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ISRG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
   <si>
     <t>ISRG</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2892300</v>
+      </c>
+      <c r="E8" s="3">
         <v>2770800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2866200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2505100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2440000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2253400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2413500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2038100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2009900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1890600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1928300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1743700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1755900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1696200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1655000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1557400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1522100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1487700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1550700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1403300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1464000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1292100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1329100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1077700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>852100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1099500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1277700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1128200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1098900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>973700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1046500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>920900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>909300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>847500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>892000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>807800</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>758800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>679600</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>756900</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>682900</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>931900</v>
+      </c>
+      <c r="E9" s="3">
         <v>940300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>961900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>842700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>822100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>795700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>771300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>664200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>637200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>645200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>650900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>576500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>584000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>583200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>544100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>505300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>498800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>478000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>489900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>431900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>440300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>389500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>433300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>353400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>349200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>361300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>381700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>342600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>339900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>304100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>310800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>278600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>277000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>253700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>258000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>239700</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>228700</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>209800</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>229700</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>195900</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1960400</v>
+      </c>
+      <c r="E10" s="3">
         <v>1830500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1904300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1662400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1617900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1457700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1642200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1373900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1372700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1245400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1277400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1167200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1171900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1113000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1110900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1052100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1023300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1009700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1060800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>971400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1023700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>902600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>895800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>724300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>502900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>738200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>896000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>785600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>759000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>669600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>735700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>642300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>632300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>593800</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>634000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>568100</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>530100</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>469800</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>527200</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>487000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,130 +1248,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>370600</v>
+      </c>
+      <c r="E12" s="3">
         <v>361900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>352900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>329400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>313300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>316200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>294700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>286000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>280100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>284500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>260100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>249400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>244400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>244900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>235700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>216200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>204800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>202000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>182300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>160200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>158300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>159100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>149000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>145000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>140100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>145200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>156600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>135900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>120800</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>144000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>119900</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>107600</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>95100</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>95500</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>87100</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>83400</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>84600</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>73500</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>69100</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>62600</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1479,19 +1496,22 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="3">
         <v>-600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-4700</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -1523,8 +1543,8 @@
       <c r="P14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1541,8 +1561,8 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>10</v>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>10</v>
@@ -1559,12 +1579,12 @@
       <c r="AB14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD14" s="3">
         <v>800</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
@@ -1572,105 +1592,108 @@
         <v>0</v>
       </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>-700</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-1800</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>42500</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>5200</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>-1200</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>9700</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>-4500</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>13500</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>5500</v>
       </c>
-      <c r="AP14" s="3" t="s">
+      <c r="AQ14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>231100</v>
+      </c>
+      <c r="E15" s="3">
         <v>200000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>156300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>160000</v>
       </c>
-      <c r="G15" s="3">
-        <v>155300</v>
-      </c>
       <c r="H15" s="3">
+        <v>164400</v>
+      </c>
+      <c r="I15" s="3">
         <v>149600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>118400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>116200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>111800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>109300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>103600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>108600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>97300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>92700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>1400</v>
-      </c>
-      <c r="S15" s="3">
-        <v>1600</v>
       </c>
       <c r="T15" s="3">
         <v>1600</v>
       </c>
       <c r="U15" s="3">
+        <v>1600</v>
+      </c>
+      <c r="V15" s="3">
         <v>1900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>1800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1700</v>
-      </c>
-      <c r="Y15" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="Z15" s="3" t="s">
         <v>10</v>
@@ -1687,8 +1710,8 @@
       <c r="AD15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE15" s="3">
-        <v>0</v>
+      <c r="AE15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AF15" s="3">
         <v>0</v>
@@ -1723,8 +1746,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1920400</v>
+      </c>
+      <c r="E17" s="3">
         <v>1915500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2001900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1745400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1696600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1675300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1678600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1460800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1442600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1421200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1478100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1277900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1292700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1308600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1282500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1158500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1124500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1079600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1100300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>960700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>952800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>875300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>913300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>807300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>771500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>816500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>880100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>762500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>739900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>721500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>714500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>607600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>631900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>570800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>563000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>527200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>498900</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>486200</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>492500</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>426500</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>971900</v>
+      </c>
+      <c r="E18" s="3">
         <v>855300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>864300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>759700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>743400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>578100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>734900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>577300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>567300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>469400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>450200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>465800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>463200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>387600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>372500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>398900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>397600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>408100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>450400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>442600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>511200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>416800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>415800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>270400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>80600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>283000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>397600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>365700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>359000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>252200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>332000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>313300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>277400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>276700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>329000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>280600</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>259900</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>193400</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>264400</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>256400</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,252 +2085,259 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E20" s="3">
         <v>1200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-9100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-13200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>24800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>5500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>27300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-11800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>25500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-10400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-14700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>22200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>3900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>9300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-5700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>3800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>18500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>15000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>32000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>20700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>84800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>26600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>25100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>34100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>33300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>32800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>27500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>26800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>21900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>18200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>13200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>12300</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>10800</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>10100</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>8700</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>11700</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>10400</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1204600</v>
+      </c>
+      <c r="E21" s="3">
         <v>1054100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1029700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>932900</v>
       </c>
-      <c r="G21" s="3">
-        <v>873900</v>
-      </c>
       <c r="H21" s="3">
+        <v>883000</v>
+      </c>
+      <c r="I21" s="3">
         <v>724900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>847800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>666200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>690900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>577600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>528300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>584800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>575200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>482400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>506800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>499700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>499900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>492800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>541600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>548600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>606900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>525400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>521000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>428600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>175100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>375600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>499400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>453200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>441600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>324100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>397800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>368800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>327400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>318900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>379800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>316300</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>293900</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>224800</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>300200</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>289100</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2340,8 +2380,8 @@
       <c r="P22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2418,252 +2458,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1054600</v>
+      </c>
+      <c r="E23" s="3">
         <v>940400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>955600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>855200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>832100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>668500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>809800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>671000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>654500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>538500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>515900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>522000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>499200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>421800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>394700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>402800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>406900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>402400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>454200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>461100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>526200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>448800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>436500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>355200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>107200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>308100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>431700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>399000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>391800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>279700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>358800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>335200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>295600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>289900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>341300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>291400</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>270000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>202100</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>276100</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>266800</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>231400</v>
+      </c>
+      <c r="E24" s="3">
         <v>114400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>156100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>146000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>167900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-35200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>121800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>123000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-8900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-94800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>102200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>73200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>61000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>58000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>78100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>93300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>33000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>71500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>73900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>3200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>13600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>72900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>38400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>37000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-8100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>69000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>75400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-24300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>95100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>30800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>34600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-6500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>55000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-7200</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>47000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>21300</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>72100</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>55800</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>823200</v>
+      </c>
+      <c r="E26" s="3">
         <v>826000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>799500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>709200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>664200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>703700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>688000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>570600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>531500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>547400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>610700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>419800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>426000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>360800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>336700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>324700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>313600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>369400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>382700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>387200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>523000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>435200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>363600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>316800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>70200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>316200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>362700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>398700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>316400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>304000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>263700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>304400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>261000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>296400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>286300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>298600</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>223000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>180800</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>204000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>211000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>818100</v>
+      </c>
+      <c r="E27" s="3">
         <v>821500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>794800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>704400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>658400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>698400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>685700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>565100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>526900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>544900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>606200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>415700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>420800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>355300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>324900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>324000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>307800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>365600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>380600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>380500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>517200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>426300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>365200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>313900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>68000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>313500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>357700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>396800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>318300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>306500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>264900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>305100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>261700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>296700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>286300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>298600</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>223000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>180800</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>204000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>211000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3224,8 +3285,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>10</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>10</v>
@@ -3242,23 +3303,23 @@
       <c r="AF29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH29" s="3">
         <v>27600</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-12600</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-6400</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-9100</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-317800</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>10</v>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>9100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>13200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-24800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-5500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-27300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>11800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-25500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>10400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>14700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-22200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-3900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-9300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>5700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-3800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-18500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-15000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-32000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-20700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-84800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-26600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-25100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-34100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-33300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-32800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-27500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-26800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-21900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-18200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-13200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-12300</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-10800</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-10100</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-8700</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-11700</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-10400</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>818100</v>
+      </c>
+      <c r="E33" s="3">
         <v>821500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>794800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>704400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>658400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>698400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>685700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>565100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>526900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>544900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>606200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>415700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>420800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>355300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>324900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>324000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>307800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>365600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>380600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>380500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>517200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>426300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>365200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>313900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>68000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>313500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>357700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>396800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>318300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>306500</v>
-      </c>
-      <c r="AG33" s="3">
-        <v>292500</v>
       </c>
       <c r="AH33" s="3">
         <v>292500</v>
       </c>
       <c r="AI33" s="3">
+        <v>292500</v>
+      </c>
+      <c r="AJ33" s="3">
         <v>255300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>287600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-31500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>298600</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>223000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>180800</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>204000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>211000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>818100</v>
+      </c>
+      <c r="E35" s="3">
         <v>821500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>794800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>704400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>658400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>698400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>685700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>565100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>526900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>544900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>606200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>415700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>420800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>355300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>324900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>324000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>307800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>365600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>380600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>380500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>517200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>426300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>365200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>313900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>68000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>313500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>357700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>396800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>318300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>306500</v>
-      </c>
-      <c r="AG35" s="3">
-        <v>292500</v>
       </c>
       <c r="AH35" s="3">
         <v>292500</v>
       </c>
       <c r="AI35" s="3">
+        <v>292500</v>
+      </c>
+      <c r="AJ35" s="3">
         <v>255300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>287600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-31500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>298600</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>223000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>180800</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>204000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>211000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,496 +4305,509 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2760400</v>
+      </c>
+      <c r="E41" s="3">
         <v>2006500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3368000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2806600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3403100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2573800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2027400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2413300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3036700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2839500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2750100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3602000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3435400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2143000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1581200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1538000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1536100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1103100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1290900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1346700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1615500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1401800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1622600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1370600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2035600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1223800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1167600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>969600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>790300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>875700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>857900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1008300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1203500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>974700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>648200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>875000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>696500</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>708600</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1036600</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>1021600</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2455800</v>
+      </c>
+      <c r="E42" s="3">
         <v>2510800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2566900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2102200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1923400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1937500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1985900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1818400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1720500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1960600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2473100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2873700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2363800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2549200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>2672200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>2902500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>3026400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>3002400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>3050300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>2883900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>2918100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>3234700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>3630000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>3482200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>2452700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>2029600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>2054100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>1928000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1928100</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1933000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>2205200</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>2127600</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1729000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1542600</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1312400</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>1271800</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>1126900</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>756200</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>1518000</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>1193700</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1774700</v>
+      </c>
+      <c r="E43" s="3">
         <v>1711100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1628200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1383900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1394200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1349400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1356800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1290000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1243200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1260400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1267500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1097100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1038800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1057400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>942100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>849600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>838500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>906100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>782700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>695000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>699900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>654300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>645500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>588600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>508800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>527600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>645200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>639000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>633400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>547600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>682300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>580400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>532500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>474900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>507900</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>468000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>481100</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>412900</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>430200</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>432000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2028700</v>
+      </c>
+      <c r="E44" s="3">
         <v>1945100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1840000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1781900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1667000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1553600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1487200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1481700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1383900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1299300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1220600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1147500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1005200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>946600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>893200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>837100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>724000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>653000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>587100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>584900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>569700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>576800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>601500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>662900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>645500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>620300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>595500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>579600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>512800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>468300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>409000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>370100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>331500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>283600</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>241200</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>225200</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>214200</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>213500</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>182300</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>183500</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4751,574 +4850,589 @@
       <c r="P45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R45" s="3">
         <v>164300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>165900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>167500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>138600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>133900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>217500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>213400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>198800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>126300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>196000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>256400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>290200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>200200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>200800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>207000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>200400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>178800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>166200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>189600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>105900</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>99200</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>88900</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>123500</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>76500</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>83300</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>80600</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9542700</v>
+      </c>
+      <c r="E46" s="3">
         <v>8809500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9779500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8525300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8745900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7657800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7111000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7215600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7654300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7632700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7888000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8902900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8031800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6877000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6253000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6293100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6292500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5803200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5844900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5728000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6016600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6066400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6625900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6300300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>5899000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4691500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4662600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4317000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4071600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4025000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4333200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4252600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>3986100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>3381700</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>2808900</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>2928900</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>2642200</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>2167700</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>3250400</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>2911400</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3538400</v>
+      </c>
+      <c r="E47" s="3">
         <v>3585700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3220900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3632200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4292000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>4675000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>4903700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>4174900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3018600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2593900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2194500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1118400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1400300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1950000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2623600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3078100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3738000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4416200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4415500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4131500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>3295600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>2673000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1757700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1643200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1586500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2642700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2623500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2533000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2429800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2255900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1771300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1434600</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1327100</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1550900</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1885900</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>1655200</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>1599900</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>1682000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>2283300</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>2346000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5551500</v>
+      </c>
+      <c r="E48" s="3">
         <v>5447900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5493200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5150900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4985300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4799000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4783000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4433000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4116800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3799600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3616900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3077000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2830800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2580200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2456400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2243700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2109300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1968200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1876400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1737900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1651200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1592900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1577300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1509700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1450300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1369200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1347300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1210800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1105200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1009600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>812000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>746400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>688800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>661900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>613100</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>584800</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>540100</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>497400</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>458400</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>447300</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>778600</v>
+      </c>
+      <c r="E49" s="3">
         <v>786700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>387400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>362600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>366600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>367100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>370500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>373600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>376700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>382000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>387800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>389900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>395800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>393400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>398300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>405300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>415300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>407300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>414100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>421500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>428300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>431700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>414100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>425200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>437800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>452400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>419300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>335200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>303500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>306100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>240600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>473500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>432200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>404900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>396900</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>355900</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>353500</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>341300</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>343900</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>336900</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>579700</v>
+      </c>
+      <c r="E52" s="3">
         <v>549500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>180200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>498300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>492600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>455800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>136900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>338800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>319700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>292700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>92700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>278100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>315900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>321000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1242700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1240600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1150100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1083500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1004100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>915700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>905300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>776400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>793900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>739100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>730000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>735300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>680500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>735300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>621500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>638300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>689600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>411500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>415400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>426800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>72000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>119800</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>115100</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>119600</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>150900</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>133100</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>20876600</v>
+      </c>
+      <c r="E54" s="3">
         <v>20111000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>20458700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>19351800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>20163200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>19220400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>18743200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17743400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>16649900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>15828000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>15441500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14712700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>13903300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>13053200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>12974000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>13260800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>13705200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>13678400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>13555000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>12934600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>12297000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>11540400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>11168900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>10617500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>10103600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>9891100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>9733200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>9131300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>8531600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>8234900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>7846700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>7318600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>6849600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>6426200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>5776800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>5644600</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>5250800</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>4808000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>6486900</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>6174700</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,130 +6145,134 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>277200</v>
+      </c>
+      <c r="E57" s="3">
         <v>332900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>255100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>291200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>266800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>276200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>193400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>218700</v>
-      </c>
-      <c r="K57" s="3">
-        <v>194400</v>
       </c>
       <c r="L57" s="3">
         <v>194400</v>
       </c>
       <c r="M57" s="3">
+        <v>194400</v>
+      </c>
+      <c r="N57" s="3">
         <v>188700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>196200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>199700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>164100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>147000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>164200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>149700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>128100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>121200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>120000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>117900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>103100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>81600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>116000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>108900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>133400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>123500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>132400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>129600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>130600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>100700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>96400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>102200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>96300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>82500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>80400</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>74200</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>74000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>68500</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>60600</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -6146,11 +6280,11 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>39000</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
@@ -6158,11 +6292,11 @@
         <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>33500</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
@@ -6170,11 +6304,11 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>25300</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
@@ -6259,252 +6393,261 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>774500</v>
+      </c>
+      <c r="E59" s="3">
         <v>771800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>690400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>690900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>649300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>632500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>680400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>769100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>689000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>652400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>700800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>845200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>752800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>617600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1275100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1069200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1025300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>984100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1028600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>907300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>886700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>801500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>883600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>778700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>815900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>812500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>906700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>798500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>677900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>609600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>719900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>606900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>564200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>484900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>749800</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>535300</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>525600</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>484200</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>528000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>467500</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1922900</v>
+      </c>
+      <c r="E60" s="3">
         <v>1911000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2006200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1803200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1692600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1538100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1745300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1676800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1487500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1375100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1658700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1676400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1538400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1307400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1422100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1233400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1175000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1112200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1149800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1027300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1004600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>904600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>965200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>894700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>924800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>945900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1030200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>930900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>807500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>740200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>820600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>703300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>666400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>581200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>662800</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>615700</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>599800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>558200</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>596500</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>528100</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -6512,11 +6655,11 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>131900</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
         <v>0</v>
       </c>
@@ -6524,11 +6667,11 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>112500</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -6536,11 +6679,11 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>64500</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -6625,130 +6768,136 @@
       <c r="AP61" s="3">
         <v>0</v>
       </c>
+      <c r="AQ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>543400</v>
+      </c>
+      <c r="E62" s="3">
         <v>498800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>287500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>427100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>445700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>411000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>301700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>329500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>322400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>356300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>275400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>370300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>359800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>406900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>439300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>453400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>447800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>409300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>453700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>447800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>412900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>445600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>444600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>436100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>412400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>414700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>418300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>423300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>444500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>454300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>338600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>326800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>314000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>338600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>660700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>69000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>128700</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>122300</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>112600</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>104800</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2578900</v>
+      </c>
+      <c r="E66" s="3">
         <v>2513800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2517000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2309700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2210100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2012700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2213600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2065900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1853400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1781600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2044200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2089200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1943600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1759000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1932100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1745400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1682200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1576100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1653900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1523700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1459500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1386900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1437400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1359700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1363100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1384400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1469400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1369900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1266300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1210700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1167900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1038000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>989000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>929100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>998000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>686700</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>728500</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>680500</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>709100</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>632900</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>6837200</v>
+      </c>
+      <c r="E72" s="3">
         <v>6397700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7011800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>6424000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7605500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7139400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6803300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>6129800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5581700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5067900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4743000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4209200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3807700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3397400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3500100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>4017800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>4682800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>4858000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>4760900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>4390100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>4022700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>3514700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>3261300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2937200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2633000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2570900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2494500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2142600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1819000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1696000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1521700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1234000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>948100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>698000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>115000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>776600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>482300</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>263300</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>1574900</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>1402800</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18168400</v>
+      </c>
+      <c r="E76" s="3">
         <v>17474500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>17824000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16929700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>17845700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>17106400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16433700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>15583300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14708300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13962600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13307600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>12539000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11879100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11217700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>11041900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>11515400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>12023000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>12102300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>11901100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>11410900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>10837500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>10153500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>9731500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>9257800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>8740500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>8506700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>8263800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>7761400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>7265300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>7024200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6678800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6280600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>5860600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>5497100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>4778800</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>4957900</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>4522300</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>4127500</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>5777800</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>5541800</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>818100</v>
+      </c>
+      <c r="E81" s="3">
         <v>821500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>794800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>704400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>658400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>698400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>685700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>565100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>526900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>544900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>606200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>415700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>420800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>355300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>324900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>324000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>307800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>365600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>380600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>380500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>517200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>426300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>365200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>313900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>68000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>313500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>357700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>396800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>318300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>306500</v>
-      </c>
-      <c r="AG81" s="3">
-        <v>292500</v>
       </c>
       <c r="AH81" s="3">
         <v>292500</v>
       </c>
       <c r="AI81" s="3">
+        <v>292500</v>
+      </c>
+      <c r="AJ81" s="3">
         <v>255300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>287600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-31500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>298600</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>223000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>180800</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>204000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>211000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>161200</v>
+      </c>
+      <c r="E83" s="3">
         <v>146200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>115300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>112700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>106800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>104200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>98500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>103500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>92300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>87700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>86600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>81900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>79800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>77700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>105700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>89000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>86800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>84300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>80900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>82000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>75600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>71700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>79800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>69200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>63800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>63400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>63800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>50900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>46700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>41600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>36300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>31000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>29100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>26400</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>27600</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>24900</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>23900</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>22700</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>24100</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>22300</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1061000</v>
+      </c>
+      <c r="E89" s="3">
         <v>911900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>892500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>841000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>715400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>581600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>822600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>706500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>620500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>265400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>228300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>548400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>665700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>371400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>437900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>383200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>446700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>223000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>567700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>501400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>542700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>477600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>627500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>274600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>229900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>352800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>552700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>396300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>316000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>333200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>338100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>319800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>231500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>280200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>332000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>353900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>216500</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>241500</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>329700</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>268800</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-112600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-103300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-162500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-105400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-155300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-116600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-312000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-247900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-309400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-241900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-435500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-256300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-178300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-194100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-137700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-169100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-130500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-95100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-150900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-68300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-75700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-58600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-61900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-64400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-110000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-105200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-142000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-86700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-82100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-114800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-55500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-47000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-44800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-40100</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-31000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-51400</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-55300</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-53000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-35600</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-30200</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-914500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-209400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>401000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>260700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>213500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1264200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1413000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-467100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-128500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1044200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-446600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>557600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>573100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>574800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>544500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>466200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-214700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-641000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-838800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-384700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-597000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-334300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1025900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>536700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-117100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-406200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-216600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-222700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-308900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-486300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-572600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-44300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>53600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-315800</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-260000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-353800</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>1308300</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-309000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-541300</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,8 +10455,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10266,8 +10500,8 @@
       <c r="P96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10344,8 +10578,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-287900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1353700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-137500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1843000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-147800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-235800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>49400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>98200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>50000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-46700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-31500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>61800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>63300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-381200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-963500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-926800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-482100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-199900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>18600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>68300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>58300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-102200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-39800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>85200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>47600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-178700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>50800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-178600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-41800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>33700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>57700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>43200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-8300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-243100</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>83600</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>124700</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-1878300</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-100</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>109700</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-4500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>8300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-12200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-3700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>6800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-5400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>5200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>3800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-2500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>2200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>3800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-3400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-400</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>-800</v>
       </c>
       <c r="AB101" s="3">
         <v>-800</v>
       </c>
       <c r="AC101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AD101" s="3">
         <v>700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>1000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>100</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>1000</v>
-      </c>
-      <c r="AM101" s="3">
-        <v>500</v>
       </c>
       <c r="AN101" s="3">
         <v>500</v>
       </c>
       <c r="AO101" s="3">
+        <v>500</v>
+      </c>
+      <c r="AP101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>753600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1355300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>557900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-597000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>829300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>554800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-383900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-620500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>199700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>97000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-852800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>165300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1291800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>565100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>46700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>433000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-187800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-55800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-268800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>212900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-220800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>252800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-666500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>813400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>56200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>198000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>179300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-85400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-18700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-113900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-195200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>228800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>326500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-226800</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>178500</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-12100</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-328000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>15000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-171900</v>
       </c>
     </row>
